--- a/utils/monday_sprint_sprint_2024-37.xlsx
+++ b/utils/monday_sprint_sprint_2024-37.xlsx
@@ -390,7 +390,7 @@
     <t>26/03/2024</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>Março</t>
@@ -3200,7 +3200,7 @@
         <v>56</v>
       </c>
       <c r="Q12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
@@ -3220,7 +3220,7 @@
         <v>21</v>
       </c>
       <c r="Q13">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
@@ -3294,7 +3294,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>44</v>
@@ -3308,7 +3308,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>50</v>
@@ -3322,7 +3322,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>51</v>
@@ -3336,7 +3336,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>120</v>

--- a/utils/monday_sprint_sprint_2024-37.xlsx
+++ b/utils/monday_sprint_sprint_2024-37.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="181">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>26140</t>
+    <t>6704189539</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>24/05/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>30/05/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,16 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>24256</t>
+    <t>6706084705</t>
   </si>
   <si>
     <t>Mocup - Sistema GIQ</t>
   </si>
   <si>
-    <t>25402</t>
+    <t>08/06/2024</t>
+  </si>
+  <si>
+    <t>6446688009</t>
   </si>
   <si>
     <t>Integração da Abertura da CPC e geração da OTF - Parte I</t>
@@ -123,7 +126,7 @@
     <t>Abril</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>6363238946</t>
   </si>
   <si>
     <t>Grupo de Maquinas Usinagem</t>
@@ -135,10 +138,13 @@
     <t>01/04/2024</t>
   </si>
   <si>
+    <t>09/06/2024</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>25418</t>
+    <t>6727553373</t>
   </si>
   <si>
     <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
@@ -147,6 +153,9 @@
     <t>29/05/2024</t>
   </si>
   <si>
+    <t>05/06/2024</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
@@ -207,13 +216,13 @@
     <t>Verificar inconsistências, caixas cadastradas com os dados já cadastrados no CPP</t>
   </si>
   <si>
-    <t>26120</t>
+    <t>6704224409</t>
   </si>
   <si>
     <t>Base de Cálculo crédito de PIS e COFINS - Fretes</t>
   </si>
   <si>
-    <t>26065</t>
+    <t>6680063640</t>
   </si>
   <si>
     <t>TEMPO PLANEJADO DO ROTEIRO PARA TELA TCPPHOR</t>
@@ -225,7 +234,7 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>25175</t>
+    <t>6715422303</t>
   </si>
   <si>
     <t>Agrupar apontamento por sequencia</t>
@@ -234,55 +243,64 @@
     <t>27/05/2024</t>
   </si>
   <si>
-    <t>26064</t>
+    <t>6680076213</t>
   </si>
   <si>
     <t>ROTEIRO PRELIMINAR NO AP-119 COM TEMPOS</t>
   </si>
   <si>
-    <t>26114</t>
+    <t>06/06/2024</t>
+  </si>
+  <si>
+    <t>6704254884</t>
   </si>
   <si>
     <t>Sense estoque por período</t>
   </si>
   <si>
-    <t>26055</t>
+    <t>04/06/2024</t>
+  </si>
+  <si>
+    <t>6680100775</t>
   </si>
   <si>
     <t>Etapa de Pintura</t>
   </si>
   <si>
-    <t>26040</t>
+    <t>6680133908</t>
   </si>
   <si>
     <t>EDITAR ROMANEIO DE CONJUNTO</t>
   </si>
   <si>
-    <t>26027</t>
+    <t>02/06/2024</t>
+  </si>
+  <si>
+    <t>6680149782</t>
   </si>
   <si>
     <t>AJUSTES APONTAMENTO ELETRONICO</t>
   </si>
   <si>
-    <t>26072</t>
+    <t>6680004348</t>
   </si>
   <si>
     <t>CRIAR LINHA NO APONTAMENTO ELETRÔNICO DOS ESCARFADORES - CANAL DE ALIMENTADOR ALTO</t>
   </si>
   <si>
-    <t>26187</t>
+    <t>6706350810</t>
   </si>
   <si>
     <t>Relatório de processos - 24929</t>
   </si>
   <si>
-    <t>24612</t>
+    <t>6706731118</t>
   </si>
   <si>
     <t>Erro de dados</t>
   </si>
   <si>
-    <t>24266</t>
+    <t>6706991140</t>
   </si>
   <si>
     <t>Correção</t>
@@ -291,67 +309,70 @@
     <t>Relação Invoices - Status</t>
   </si>
   <si>
-    <t>26118</t>
+    <t>28/05/2024</t>
+  </si>
+  <si>
+    <t>6704238403</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE DEPENDÊNCIAS - SETORES PRÉ-PRODUTIVOS</t>
   </si>
   <si>
-    <t>26017</t>
+    <t>6680169481</t>
   </si>
   <si>
     <t>Carteira em excel - nome das peças em português e outro idioma</t>
   </si>
   <si>
-    <t>26003</t>
+    <t>6680210039</t>
   </si>
   <si>
     <t>Descrição da peça em português na OTF</t>
   </si>
   <si>
-    <t>25821</t>
+    <t>6713391758</t>
   </si>
   <si>
     <t>Tabelas Manutenção - MTBR</t>
   </si>
   <si>
-    <t>26176</t>
+    <t>6704103146</t>
   </si>
   <si>
     <t>Bloquear unir amostra de cliente na etiqueta.</t>
   </si>
   <si>
-    <t>22639</t>
+    <t>6707008369</t>
   </si>
   <si>
     <t>Saldo do Deposito / Controle de Embalagem</t>
   </si>
   <si>
-    <t>26151</t>
+    <t>6704176733</t>
   </si>
   <si>
     <t>[COMPRAS] Criar botão para acelerar a aprovação dos pedidos</t>
   </si>
   <si>
-    <t>26183</t>
+    <t>6707088153</t>
   </si>
   <si>
     <t>OC 343317</t>
   </si>
   <si>
-    <t>25188</t>
+    <t>6706739417</t>
   </si>
   <si>
     <t>Erro no apontamento</t>
   </si>
   <si>
-    <t>26155</t>
+    <t>6704130904</t>
   </si>
   <si>
     <t>Sistema Ronda</t>
   </si>
   <si>
-    <t>25899</t>
+    <t>6619455824</t>
   </si>
   <si>
     <t>Fluxo de produção - Criação de conserto</t>
@@ -360,55 +381,58 @@
     <t>10/05/2024</t>
   </si>
   <si>
-    <t>25990</t>
+    <t>6620608900</t>
   </si>
   <si>
     <t>Inclusão de novos tipos de OTF</t>
   </si>
   <si>
-    <t>21843</t>
+    <t>6715094539</t>
   </si>
   <si>
     <t>Alteração Extrações de Cálculo Novo Custeio - USINAGEM - Frete s/ Beneficiamento de Terceiros</t>
   </si>
   <si>
-    <t>25363</t>
+    <t>6715094646</t>
   </si>
   <si>
     <t>Apontamento eletrônico manipuladores</t>
   </si>
   <si>
-    <t>25337</t>
+    <t>6715094707</t>
   </si>
   <si>
     <t>Alteração Etiqueta Impact/Westpower</t>
   </si>
   <si>
-    <t>25802</t>
+    <t>6715094985</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO</t>
   </si>
   <si>
-    <t>25686</t>
+    <t>6715095013</t>
   </si>
   <si>
     <t>Sistema Solicitação de Embalagens / Inventário de Embalagens - (Chamado Matriz)</t>
   </si>
   <si>
-    <t>25919</t>
+    <t>6715095089</t>
+  </si>
+  <si>
+    <t>6715095115</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO FLUXOS ROBÔ REBARBAÇÃO</t>
   </si>
   <si>
-    <t>25784</t>
+    <t>6715094529</t>
   </si>
   <si>
     <t>Aplicativo mobile para sistema de manutenção</t>
   </si>
   <si>
-    <t>26306</t>
+    <t>6794343623</t>
   </si>
   <si>
     <t>Relatório Auditoria</t>
@@ -423,6 +447,9 @@
     <t>25311</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Controle de Transferências de Exportação</t>
   </si>
   <si>
@@ -447,7 +474,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-37</t>
+    <t>Abr/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1089,7 +1116,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1106,7 +1133,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1118,10 +1145,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1133,7 +1160,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -1145,62 +1172,62 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1212,10 +1239,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1227,19 +1254,19 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1247,7 +1274,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1259,10 +1286,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1274,10 +1301,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1286,15 +1313,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1306,25 +1333,25 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1333,92 +1360,92 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1427,45 +1454,45 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1474,45 +1501,45 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1521,15 +1548,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1541,10 +1568,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1559,7 +1586,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1576,7 +1603,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1588,10 +1615,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1603,10 +1630,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1615,7 +1642,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1623,25 +1650,25 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1650,10 +1677,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1670,7 +1697,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1682,10 +1709,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1697,19 +1724,19 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1717,7 +1744,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1729,10 +1756,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1747,7 +1774,7 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1764,7 +1791,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1776,10 +1803,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1791,10 +1818,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1803,7 +1830,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -1811,7 +1838,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1823,10 +1850,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1838,10 +1865,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1850,7 +1877,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1858,7 +1885,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1870,10 +1897,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1885,10 +1912,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1897,7 +1924,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1905,7 +1932,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1917,10 +1944,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1932,10 +1959,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1944,7 +1971,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -1952,7 +1979,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1964,10 +1991,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1982,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1999,7 +2026,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2011,10 +2038,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2029,7 +2056,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2046,22 +2073,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2076,7 +2103,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2093,7 +2120,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2105,10 +2132,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2123,7 +2150,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2140,7 +2167,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2152,10 +2179,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2167,7 +2194,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2179,7 +2206,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2187,7 +2214,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2199,10 +2226,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2214,10 +2241,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2226,7 +2253,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2234,7 +2261,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2246,10 +2273,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2261,10 +2288,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2281,7 +2308,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2293,10 +2320,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2311,7 +2338,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2328,7 +2355,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2340,10 +2367,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2358,7 +2385,7 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2375,7 +2402,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2387,10 +2414,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2405,7 +2432,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2422,22 +2449,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2452,7 +2479,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2469,22 +2496,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2499,10 +2526,10 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
@@ -2516,7 +2543,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2528,10 +2555,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2546,7 +2573,7 @@
         <v>23</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2563,7 +2590,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2575,10 +2602,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2590,10 +2617,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2602,7 +2629,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2610,7 +2637,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2622,10 +2649,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2637,10 +2664,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2649,7 +2676,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2657,7 +2684,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2669,10 +2696,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2684,10 +2711,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2704,7 +2731,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2716,10 +2743,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2731,13 +2758,13 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -2751,7 +2778,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2763,10 +2790,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2778,10 +2805,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2798,7 +2825,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2810,10 +2837,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2825,10 +2852,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2845,7 +2872,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2857,10 +2884,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2872,7 +2899,7 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>24</v>
@@ -2892,7 +2919,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2904,10 +2931,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2919,10 +2946,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2939,7 +2966,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2951,10 +2978,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2966,10 +2993,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2986,7 +3013,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2998,10 +3025,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3013,10 +3040,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3033,7 +3060,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3045,13 +3072,13 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -3060,10 +3087,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3072,54 +3099,54 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3138,23 +3165,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3162,16 +3189,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3182,15 +3209,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>677</v>
+        <v>28.27</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3203,7 +3230,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -3211,7 +3238,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3242,12 +3269,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B2">
         <v>45</v>
@@ -3261,35 +3288,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>677</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3297,7 +3324,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -3306,13 +3333,13 @@
         <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3324,27 +3351,27 @@
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -3356,21 +3383,27 @@
         <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3382,33 +3415,33 @@
         <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Q12">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3417,32 +3450,32 @@
         <v>27</v>
       </c>
       <c r="Q13">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="P14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3450,7 +3483,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3458,7 +3491,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3466,10 +3499,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3477,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3485,142 +3518,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="F21" s="2">
-        <v>662</v>
+        <v>705</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2">
         <v>55</v>
       </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
